--- a/SECS Flow.xlsx
+++ b/SECS Flow.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>EAP</t>
   </si>
@@ -56,9 +56,6 @@
     <t>S7F22 Formatted Process Program Send</t>
   </si>
   <si>
-    <t>S7F23 Formatted Process Program Data</t>
-  </si>
-  <si>
     <t>S2F41 Host Remote Command Send</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,6 +77,14 @@
   </si>
   <si>
     <t>S6F11 PP_SELECTED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S2F41 Host Command Acknowledge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S7F23 Formatted Process Program Acknowledge</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -207,16 +212,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -225,14 +221,23 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1167,286 +1172,286 @@
       </c>
     </row>
     <row r="5" spans="1:24" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="7" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="8" t="s">
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
     </row>
     <row r="6" spans="1:24" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="G6" s="9"/>
-      <c r="M6" s="11"/>
-      <c r="O6" s="9"/>
-      <c r="U6" s="11"/>
-      <c r="W6" s="9"/>
+      <c r="G6" s="6"/>
+      <c r="M6" s="8"/>
+      <c r="O6" s="6"/>
+      <c r="U6" s="8"/>
+      <c r="W6" s="6"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G7" s="10"/>
-      <c r="M7" s="12"/>
-      <c r="O7" s="10"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12" t="s">
+      <c r="G7" s="7"/>
+      <c r="M7" s="9"/>
+      <c r="O7" s="7"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="U7" s="12"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="10"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="7"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G8" s="10"/>
-      <c r="M8" s="12"/>
-      <c r="O8" s="10"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="10"/>
+      <c r="G8" s="7"/>
+      <c r="M8" s="9"/>
+      <c r="O8" s="7"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="7"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G9" s="10"/>
-      <c r="M9" s="12"/>
-      <c r="O9" s="10" t="s">
+      <c r="G9" s="7"/>
+      <c r="M9" s="9"/>
+      <c r="O9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="Q9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="W9" s="10"/>
+      <c r="Q9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="W9" s="7"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G10" s="10"/>
-      <c r="M10" s="12"/>
-      <c r="O10" s="10"/>
-      <c r="U10" s="12"/>
-      <c r="W10" s="10"/>
+      <c r="G10" s="7"/>
+      <c r="M10" s="9"/>
+      <c r="O10" s="7"/>
+      <c r="U10" s="9"/>
+      <c r="W10" s="7"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G11" s="10"/>
-      <c r="M11" s="12"/>
-      <c r="O11" s="10"/>
+      <c r="G11" s="7"/>
+      <c r="M11" s="9"/>
+      <c r="O11" s="7"/>
       <c r="S11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="U11" s="12"/>
-      <c r="W11" s="10"/>
+        <v>11</v>
+      </c>
+      <c r="U11" s="9"/>
+      <c r="W11" s="7"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G12" s="10"/>
-      <c r="M12" s="12"/>
-      <c r="O12" s="10"/>
-      <c r="U12" s="12"/>
-      <c r="W12" s="10"/>
+      <c r="G12" s="7"/>
+      <c r="M12" s="9"/>
+      <c r="O12" s="7"/>
+      <c r="U12" s="9"/>
+      <c r="W12" s="7"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G13" s="10"/>
-      <c r="M13" s="12"/>
-      <c r="O13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="U13" s="12"/>
-      <c r="W13" s="10"/>
+      <c r="G13" s="7"/>
+      <c r="M13" s="9"/>
+      <c r="O13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U13" s="9"/>
+      <c r="W13" s="7"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G14" s="10"/>
-      <c r="M14" s="12"/>
-      <c r="O14" s="10"/>
-      <c r="U14" s="12"/>
-      <c r="W14" s="10"/>
+      <c r="G14" s="7"/>
+      <c r="M14" s="9"/>
+      <c r="O14" s="7"/>
+      <c r="U14" s="9"/>
+      <c r="W14" s="7"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G15" s="10"/>
-      <c r="M15" s="12"/>
-      <c r="O15" s="10"/>
+      <c r="G15" s="7"/>
+      <c r="M15" s="9"/>
+      <c r="O15" s="7"/>
       <c r="T15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="W15" s="10"/>
+      <c r="W15" s="7"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G16" s="10"/>
-      <c r="M16" s="12"/>
-      <c r="O16" s="10"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="10"/>
+      <c r="G16" s="7"/>
+      <c r="M16" s="9"/>
+      <c r="O16" s="7"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="7"/>
     </row>
     <row r="17" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G17" s="10"/>
-      <c r="M17" s="12"/>
-      <c r="O17" s="10" t="s">
+      <c r="G17" s="7"/>
+      <c r="M17" s="9"/>
+      <c r="O17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="U17" s="12"/>
-      <c r="W17" s="10"/>
+      <c r="U17" s="9"/>
+      <c r="W17" s="7"/>
     </row>
     <row r="18" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G18" s="10"/>
-      <c r="M18" s="12"/>
-      <c r="O18" s="10"/>
-      <c r="U18" s="12"/>
-      <c r="W18" s="10"/>
+      <c r="G18" s="7"/>
+      <c r="M18" s="9"/>
+      <c r="O18" s="7"/>
+      <c r="U18" s="9"/>
+      <c r="W18" s="7"/>
     </row>
     <row r="19" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G19" s="10"/>
-      <c r="M19" s="12"/>
-      <c r="O19" s="10"/>
-      <c r="R19" s="14" t="s">
+      <c r="G19" s="7"/>
+      <c r="M19" s="9"/>
+      <c r="O19" s="7"/>
+      <c r="R19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="10"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="7"/>
     </row>
     <row r="20" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G20" s="10"/>
-      <c r="M20" s="12"/>
-      <c r="O20" s="10"/>
-      <c r="U20" s="12"/>
-      <c r="W20" s="10"/>
+      <c r="G20" s="7"/>
+      <c r="M20" s="9"/>
+      <c r="O20" s="7"/>
+      <c r="U20" s="9"/>
+      <c r="W20" s="7"/>
     </row>
     <row r="21" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G21" s="10"/>
-      <c r="M21" s="12"/>
-      <c r="O21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="W21" s="10"/>
+      <c r="G21" s="7"/>
+      <c r="M21" s="9"/>
+      <c r="O21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="W21" s="7"/>
     </row>
     <row r="22" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G22" s="10"/>
-      <c r="M22" s="12"/>
-      <c r="O22" s="10"/>
-      <c r="U22" s="12"/>
-      <c r="W22" s="10"/>
+      <c r="G22" s="7"/>
+      <c r="M22" s="9"/>
+      <c r="O22" s="7"/>
+      <c r="U22" s="9"/>
+      <c r="W22" s="7"/>
     </row>
     <row r="23" spans="7:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G23" s="10"/>
-      <c r="J23" s="14" t="s">
+      <c r="G23" s="7"/>
+      <c r="J23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="7"/>
+      <c r="R23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="7"/>
+    </row>
+    <row r="24" spans="7:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G24" s="7"/>
+      <c r="M24" s="9"/>
+      <c r="O24" s="7"/>
+      <c r="W24" s="7"/>
+    </row>
+    <row r="25" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="10"/>
-      <c r="R23" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="10"/>
-    </row>
-    <row r="24" spans="7:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G24" s="10"/>
-      <c r="M24" s="12"/>
-      <c r="O24" s="10"/>
-      <c r="W24" s="10"/>
-    </row>
-    <row r="25" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G25" s="10" t="s">
+      <c r="M25" s="9"/>
+      <c r="O25" s="7"/>
+      <c r="U25" s="9"/>
+      <c r="W25" s="7"/>
+    </row>
+    <row r="26" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G26" s="7"/>
+      <c r="M26" s="9"/>
+      <c r="O26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="U26" s="9"/>
+      <c r="W26" s="7"/>
+    </row>
+    <row r="27" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G27" s="7"/>
+      <c r="M27" s="9"/>
+      <c r="O27" s="7"/>
+      <c r="U27" s="9"/>
+      <c r="W27" s="7"/>
+    </row>
+    <row r="28" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G28" s="7"/>
+      <c r="M28" s="9"/>
+      <c r="O28" s="7"/>
+      <c r="U28" s="9"/>
+      <c r="W28" s="7"/>
+    </row>
+    <row r="29" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G29" s="7"/>
+      <c r="M29" s="9"/>
+      <c r="O29" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="M25" s="12"/>
-      <c r="O25" s="10"/>
-      <c r="U25" s="12"/>
-      <c r="W25" s="10"/>
-    </row>
-    <row r="26" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G26" s="10"/>
-      <c r="M26" s="12"/>
-      <c r="O26" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="U26" s="12"/>
-      <c r="W26" s="10"/>
-    </row>
-    <row r="27" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G27" s="10"/>
-      <c r="M27" s="12"/>
-      <c r="O27" s="10"/>
-      <c r="U27" s="12"/>
-      <c r="W27" s="10"/>
-    </row>
-    <row r="28" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G28" s="10"/>
-      <c r="M28" s="12"/>
-      <c r="O28" s="10"/>
-      <c r="U28" s="12"/>
-      <c r="W28" s="10"/>
-    </row>
-    <row r="29" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G29" s="10"/>
-      <c r="M29" s="12"/>
-      <c r="O29" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="U29" s="12"/>
-      <c r="W29" s="10"/>
+      <c r="U29" s="9"/>
+      <c r="W29" s="7"/>
     </row>
     <row r="30" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G30" s="10"/>
-      <c r="M30" s="12"/>
-      <c r="O30" s="10"/>
-      <c r="U30" s="12"/>
-      <c r="W30" s="10"/>
+      <c r="G30" s="7"/>
+      <c r="M30" s="9"/>
+      <c r="O30" s="7"/>
+      <c r="U30" s="9"/>
+      <c r="W30" s="7"/>
     </row>
     <row r="31" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G31" s="10"/>
-      <c r="M31" s="12"/>
-      <c r="O31" s="10"/>
-      <c r="U31" s="12"/>
-      <c r="W31" s="10"/>
+      <c r="G31" s="7"/>
+      <c r="M31" s="9"/>
+      <c r="O31" s="7"/>
+      <c r="U31" s="9"/>
+      <c r="W31" s="7"/>
     </row>
     <row r="32" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G32" s="10"/>
-      <c r="M32" s="12"/>
-      <c r="O32" s="10"/>
-      <c r="U32" s="12"/>
-      <c r="W32" s="10"/>
+      <c r="G32" s="7"/>
+      <c r="M32" s="9"/>
+      <c r="O32" s="7"/>
+      <c r="U32" s="9"/>
+      <c r="W32" s="7"/>
     </row>
     <row r="33" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="G33" s="10"/>
-      <c r="M33" s="12"/>
-      <c r="O33" s="10"/>
-      <c r="U33" s="12"/>
-      <c r="W33" s="10"/>
+      <c r="G33" s="7"/>
+      <c r="M33" s="9"/>
+      <c r="O33" s="7"/>
+      <c r="U33" s="9"/>
+      <c r="W33" s="7"/>
     </row>
     <row r="34" spans="7:23" x14ac:dyDescent="0.25">
-      <c r="M34" s="12"/>
-      <c r="U34" s="12"/>
+      <c r="M34" s="9"/>
+      <c r="U34" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/SECS Flow.xlsx
+++ b/SECS Flow.xlsx
@@ -53,9 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>S7F22 Formatted Process Program Send</t>
-  </si>
-  <si>
     <t>S2F41 Host Remote Command Send</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,7 +81,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>S7F23 Formatted Process Program Acknowledge</t>
+    <t>S7F23 Formatted Process Program Send</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S7F24 Formatted Process Program Acknowledge</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1250,7 +1251,7 @@
       <c r="M11" s="9"/>
       <c r="O11" s="7"/>
       <c r="S11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U11" s="9"/>
       <c r="W11" s="7"/>
@@ -1266,7 +1267,7 @@
       <c r="G13" s="7"/>
       <c r="M13" s="9"/>
       <c r="O13" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U13" s="9"/>
       <c r="W13" s="7"/>
@@ -1319,7 +1320,7 @@
       <c r="M19" s="9"/>
       <c r="O19" s="7"/>
       <c r="R19" s="13" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
@@ -1358,7 +1359,7 @@
     <row r="23" spans="7:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G23" s="7"/>
       <c r="J23" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
@@ -1366,7 +1367,7 @@
       <c r="N23" s="14"/>
       <c r="O23" s="7"/>
       <c r="R23" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S23" s="13"/>
       <c r="T23" s="13"/>
@@ -1382,7 +1383,7 @@
     </row>
     <row r="25" spans="7:23" x14ac:dyDescent="0.25">
       <c r="G25" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M25" s="9"/>
       <c r="O25" s="7"/>
@@ -1393,7 +1394,7 @@
       <c r="G26" s="7"/>
       <c r="M26" s="9"/>
       <c r="O26" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U26" s="9"/>
       <c r="W26" s="7"/>
@@ -1416,7 +1417,7 @@
       <c r="G29" s="7"/>
       <c r="M29" s="9"/>
       <c r="O29" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U29" s="9"/>
       <c r="W29" s="7"/>
